--- a/database/template-import-export/templates/template-perkebunan.xlsx
+++ b/database/template-import-export/templates/template-perkebunan.xlsx
@@ -28,7 +28,7 @@
     <t>Areal &amp; produksi perkebunan per kecamatan dan agregat kabupaten.</t>
   </si>
   <si>
-    <t>Dibuat otomatis: 22/9/2026, 14.21.31</t>
+    <t>Dibuat otomatis: 29/9/2026, 15.29.41</t>
   </si>
   <si>
     <t>CARA PAKAI</t>
